--- a/data/trans_bre/IP16B03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Habitat-trans_bre.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 0,0</t>
+          <t>-71,17; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,0; 0,0</t>
+          <t>-71,17; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,06</t>
+          <t>0,0; 34,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,46</t>
+          <t>0,0; 53,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,46; 0,0</t>
+          <t>-51,48; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 0,0</t>
+          <t>-75,0; 0,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16B03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16B03-Habitat-trans_bre.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 0,0</t>
+          <t>-70,17; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,17; 0,0</t>
+          <t>-70,17; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,58</t>
+          <t>0,0; 37,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,26</t>
+          <t>0,0; 60,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,48; 0,0</t>
+          <t>-44,32; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
